--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -97,18 +97,6 @@
     <t xml:space="preserve">Natales</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11102</t>
   </si>
   <si>
@@ -331,6 +319,12 @@
     <t xml:space="preserve">Pencahue</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">7102</t>
   </si>
   <si>
@@ -1042,6 +1036,12 @@
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4201</t>
   </si>
   <si>
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:23</t>
+    <t xml:space="preserve">2026-09-09 20:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2429,7 +2429,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>70.72</v>
+        <v>68.75</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>16</v>
@@ -2440,10 +2440,10 @@
         <v>2021</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>28</v>
@@ -2461,7 +2461,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>70.52</v>
+        <v>66.67</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>16</v>
@@ -2472,10 +2472,10 @@
         <v>2021</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>30</v>
@@ -2493,7 +2493,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>68.75</v>
+        <v>63.7</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>16</v>
@@ -2525,7 +2525,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>66.67</v>
+        <v>63.64</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>16</v>
@@ -2536,28 +2536,28 @@
         <v>2021</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>63.7</v>
+        <v>72.32</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>16</v>
@@ -2568,28 +2568,28 @@
         <v>2021</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>63.64</v>
+        <v>68.7</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>16</v>
@@ -2603,25 +2603,25 @@
         <v>7</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>72.32</v>
+        <v>68.62</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>16</v>
@@ -2632,10 +2632,10 @@
         <v>2021</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>44</v>
@@ -2644,16 +2644,16 @@
         <v>45</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>68.7</v>
+        <v>68.44</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>16</v>
@@ -2667,7 +2667,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>46</v>
@@ -2676,16 +2676,16 @@
         <v>47</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>68.62</v>
+        <v>68.36</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>16</v>
@@ -2699,7 +2699,7 @@
         <v>7</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>48</v>
@@ -2708,16 +2708,16 @@
         <v>49</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>68.44</v>
+        <v>68.34</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>16</v>
@@ -2728,28 +2728,28 @@
         <v>2021</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>68.36</v>
+        <v>67.75</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>16</v>
@@ -2760,28 +2760,28 @@
         <v>2021</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>68.34</v>
+        <v>67.68</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>16</v>
@@ -2792,10 +2792,10 @@
         <v>2021</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D19" s="2" t="s">
         <v>55</v>
@@ -2804,16 +2804,16 @@
         <v>56</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>67.75</v>
+        <v>67.56</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>16</v>
@@ -2824,28 +2824,28 @@
         <v>2021</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>67.68</v>
+        <v>66.52</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>16</v>
@@ -2859,25 +2859,25 @@
         <v>7</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>67.56</v>
+        <v>65.86</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>16</v>
@@ -2888,10 +2888,10 @@
         <v>2021</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>62</v>
@@ -2900,16 +2900,16 @@
         <v>63</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>66.52</v>
+        <v>64.92</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>16</v>
@@ -2920,10 +2920,10 @@
         <v>2021</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>64</v>
@@ -2932,16 +2932,16 @@
         <v>65</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>65.86</v>
+        <v>64.17</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>16</v>
@@ -2955,7 +2955,7 @@
         <v>7</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>66</v>
@@ -2964,16 +2964,16 @@
         <v>67</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>64.92</v>
+        <v>63.71</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>16</v>
@@ -2984,10 +2984,10 @@
         <v>2021</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>68</v>
@@ -2996,16 +2996,16 @@
         <v>69</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>64.17</v>
+        <v>63.62</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>16</v>
@@ -3019,7 +3019,7 @@
         <v>7</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>70</v>
@@ -3028,16 +3028,16 @@
         <v>71</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>63.71</v>
+        <v>63.52</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>16</v>
@@ -3048,10 +3048,10 @@
         <v>2021</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D27" s="2" t="s">
         <v>72</v>
@@ -3060,16 +3060,16 @@
         <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>63.62</v>
+        <v>63.25</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>16</v>
@@ -3080,10 +3080,10 @@
         <v>2021</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>74</v>
@@ -3092,16 +3092,16 @@
         <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>63.52</v>
+        <v>63.24</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>16</v>
@@ -3112,10 +3112,10 @@
         <v>2021</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3124,16 +3124,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>63.25</v>
+        <v>63.2</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>16</v>
@@ -3144,10 +3144,10 @@
         <v>2021</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3156,16 +3156,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>63.24</v>
+        <v>62.82</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>16</v>
@@ -3179,7 +3179,7 @@
         <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3188,16 +3188,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>63.2</v>
+        <v>62.77</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>16</v>
@@ -3208,10 +3208,10 @@
         <v>2021</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3220,16 +3220,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>62.82</v>
+        <v>62.66</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>16</v>
@@ -3240,10 +3240,10 @@
         <v>2021</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3252,16 +3252,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>62.77</v>
+        <v>62.45</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>16</v>
@@ -3272,10 +3272,10 @@
         <v>2021</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3284,16 +3284,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>62.66</v>
+        <v>62.38</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>16</v>
@@ -3304,10 +3304,10 @@
         <v>2021</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3316,16 +3316,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>62.45</v>
+        <v>62.05</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>16</v>
@@ -3336,10 +3336,10 @@
         <v>2021</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>54</v>
+        <v>34</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3348,16 +3348,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>62.38</v>
+        <v>61.99</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>16</v>
@@ -3368,10 +3368,10 @@
         <v>2021</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3380,16 +3380,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>62.05</v>
+        <v>61.88</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>16</v>
@@ -3400,10 +3400,10 @@
         <v>2021</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3412,16 +3412,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>61.99</v>
+        <v>61.7</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>16</v>
@@ -3432,10 +3432,10 @@
         <v>2021</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3444,16 +3444,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>61.88</v>
+        <v>61.69</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>16</v>
@@ -3464,10 +3464,10 @@
         <v>2021</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3476,16 +3476,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>61.7</v>
+        <v>61.63</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>16</v>
@@ -3499,7 +3499,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3508,16 +3508,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>61.69</v>
+        <v>61.57</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>16</v>
@@ -3531,7 +3531,7 @@
         <v>7</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3540,16 +3540,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>61.63</v>
+        <v>61.57</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>16</v>
@@ -3560,10 +3560,10 @@
         <v>2021</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3572,16 +3572,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>61.57</v>
+        <v>61.17</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>16</v>
@@ -3592,10 +3592,10 @@
         <v>2021</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3604,16 +3604,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>61.17</v>
+        <v>61.07</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>16</v>
@@ -3624,10 +3624,10 @@
         <v>2021</v>
       </c>
       <c r="B45" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3636,16 +3636,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>61.07</v>
+        <v>60.9</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>16</v>
@@ -3656,10 +3656,10 @@
         <v>2021</v>
       </c>
       <c r="B46" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
@@ -3668,16 +3668,16 @@
         <v>111</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>60.9</v>
+        <v>60.58</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>16</v>
@@ -3691,7 +3691,7 @@
         <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>112</v>
@@ -3700,16 +3700,16 @@
         <v>113</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>60.58</v>
+        <v>60.56</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>16</v>
@@ -3723,7 +3723,7 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>114</v>
@@ -3732,16 +3732,16 @@
         <v>115</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>60.56</v>
+        <v>60.4</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>16</v>
@@ -3752,10 +3752,10 @@
         <v>2021</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>116</v>
@@ -3764,16 +3764,16 @@
         <v>117</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>60.4</v>
+        <v>60.15</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>16</v>
@@ -3784,10 +3784,10 @@
         <v>2021</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>118</v>
@@ -3796,16 +3796,16 @@
         <v>119</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>60.15</v>
+        <v>60</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>16</v>
@@ -3819,7 +3819,7 @@
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>120</v>
@@ -3828,16 +3828,16 @@
         <v>121</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>60</v>
+        <v>59.89</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>16</v>
@@ -3848,10 +3848,10 @@
         <v>2021</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>122</v>
@@ -3860,16 +3860,16 @@
         <v>123</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>59.89</v>
+        <v>59.76</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>16</v>
@@ -3880,10 +3880,10 @@
         <v>2021</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>124</v>
@@ -3892,16 +3892,16 @@
         <v>125</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>59.76</v>
+        <v>59.64</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>16</v>
@@ -3912,10 +3912,10 @@
         <v>2021</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>126</v>
@@ -3924,16 +3924,16 @@
         <v>127</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>59.64</v>
+        <v>59.6</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>16</v>
@@ -3947,7 +3947,7 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>128</v>
@@ -3956,16 +3956,16 @@
         <v>129</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>59.6</v>
+        <v>59.4</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>16</v>
@@ -3976,10 +3976,10 @@
         <v>2021</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>130</v>
@@ -3988,16 +3988,16 @@
         <v>131</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>59.4</v>
+        <v>59.38</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>16</v>
@@ -4008,10 +4008,10 @@
         <v>2021</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>132</v>
@@ -4020,10 +4020,10 @@
         <v>133</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4040,10 +4040,10 @@
         <v>2021</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>134</v>
@@ -4052,16 +4052,16 @@
         <v>135</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>59.38</v>
+        <v>59.33</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>16</v>
@@ -4072,10 +4072,10 @@
         <v>2021</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>136</v>
@@ -4084,16 +4084,16 @@
         <v>137</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>59.33</v>
+        <v>59.32</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>16</v>
@@ -4107,7 +4107,7 @@
         <v>6</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>138</v>
@@ -4116,16 +4116,16 @@
         <v>139</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>59.32</v>
+        <v>58.85</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>16</v>
@@ -4136,10 +4136,10 @@
         <v>2021</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>140</v>
@@ -4148,16 +4148,16 @@
         <v>141</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>58.85</v>
+        <v>58.62</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>16</v>
@@ -4168,10 +4168,10 @@
         <v>2021</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>61</v>
+        <v>34</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>142</v>
@@ -4180,16 +4180,16 @@
         <v>143</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>58.62</v>
+        <v>58.59</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>16</v>
@@ -4200,10 +4200,10 @@
         <v>2021</v>
       </c>
       <c r="B63" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>144</v>
@@ -4212,16 +4212,16 @@
         <v>145</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>58.59</v>
+        <v>58.49</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>16</v>
@@ -4232,10 +4232,10 @@
         <v>2021</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>146</v>
@@ -4244,16 +4244,16 @@
         <v>147</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>58.49</v>
+        <v>58.27</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>16</v>
@@ -4267,7 +4267,7 @@
         <v>6</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>148</v>
@@ -4276,16 +4276,16 @@
         <v>149</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>58.27</v>
+        <v>58.19</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>16</v>
@@ -4296,10 +4296,10 @@
         <v>2021</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>150</v>
@@ -4308,16 +4308,16 @@
         <v>151</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>58.19</v>
+        <v>58.07</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>16</v>
@@ -4328,10 +4328,10 @@
         <v>2021</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>152</v>
@@ -4340,16 +4340,16 @@
         <v>153</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>58.07</v>
+        <v>58.04</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>16</v>
@@ -4360,10 +4360,10 @@
         <v>2021</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>154</v>
@@ -4372,16 +4372,16 @@
         <v>155</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>58.04</v>
+        <v>57.84</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>16</v>
@@ -4392,10 +4392,10 @@
         <v>2021</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>156</v>
@@ -4404,16 +4404,16 @@
         <v>157</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>57.84</v>
+        <v>57.79</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>16</v>
@@ -4424,10 +4424,10 @@
         <v>2021</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>158</v>
@@ -4436,16 +4436,16 @@
         <v>159</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>57.79</v>
+        <v>57.73</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>16</v>
@@ -4459,7 +4459,7 @@
         <v>6</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>160</v>
@@ -4468,16 +4468,16 @@
         <v>161</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>57.73</v>
+        <v>57.66</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>16</v>
@@ -4488,10 +4488,10 @@
         <v>2021</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>162</v>
@@ -4500,16 +4500,16 @@
         <v>163</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>57.66</v>
+        <v>57.36</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>16</v>
@@ -4520,10 +4520,10 @@
         <v>2021</v>
       </c>
       <c r="B73" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>164</v>
@@ -4532,16 +4532,16 @@
         <v>165</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>57.36</v>
+        <v>57.3</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>16</v>
@@ -4555,7 +4555,7 @@
         <v>5</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>166</v>
@@ -4564,16 +4564,16 @@
         <v>167</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>57.3</v>
+        <v>57.26</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>16</v>
@@ -4584,10 +4584,10 @@
         <v>2021</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>168</v>
@@ -4596,10 +4596,10 @@
         <v>169</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4616,10 +4616,10 @@
         <v>2021</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>170</v>
@@ -4628,16 +4628,16 @@
         <v>171</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>57.26</v>
+        <v>57.05</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>16</v>
@@ -4651,7 +4651,7 @@
         <v>6</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>172</v>
@@ -4660,16 +4660,16 @@
         <v>173</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>57.05</v>
+        <v>56.88</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>16</v>
@@ -4683,7 +4683,7 @@
         <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>174</v>
@@ -4692,16 +4692,16 @@
         <v>175</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>56.88</v>
+        <v>56.69</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>16</v>
@@ -4712,28 +4712,28 @@
         <v>2021</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>56.69</v>
+        <v>56.68</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>16</v>
@@ -4747,7 +4747,7 @@
         <v>13</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>179</v>
@@ -4756,16 +4756,16 @@
         <v>180</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>56.68</v>
+        <v>56.64</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>16</v>
@@ -4776,10 +4776,10 @@
         <v>2021</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>181</v>
@@ -4788,16 +4788,16 @@
         <v>182</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>56.64</v>
+        <v>56.56</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>16</v>
@@ -4811,7 +4811,7 @@
         <v>5</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>183</v>
@@ -4820,16 +4820,16 @@
         <v>184</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>56.56</v>
+        <v>56.39</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>16</v>
@@ -4840,10 +4840,10 @@
         <v>2021</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>185</v>
@@ -4852,16 +4852,16 @@
         <v>186</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>56.39</v>
+        <v>56.33</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>16</v>
@@ -4872,10 +4872,10 @@
         <v>2021</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>43</v>
+        <v>176</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>187</v>
@@ -4884,16 +4884,16 @@
         <v>188</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>56.33</v>
+        <v>56.32</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>16</v>
@@ -4904,10 +4904,10 @@
         <v>2021</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>189</v>
@@ -4916,16 +4916,16 @@
         <v>190</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>56.32</v>
+        <v>56.27</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>16</v>
@@ -4936,10 +4936,10 @@
         <v>2021</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>191</v>
@@ -4948,16 +4948,16 @@
         <v>192</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>56.27</v>
+        <v>56.24</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>16</v>
@@ -4968,10 +4968,10 @@
         <v>2021</v>
       </c>
       <c r="B87" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>61</v>
+        <v>39</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>193</v>
@@ -4980,16 +4980,16 @@
         <v>194</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>56.24</v>
+        <v>56.23</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>16</v>
@@ -5000,10 +5000,10 @@
         <v>2021</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>195</v>
@@ -5012,16 +5012,16 @@
         <v>196</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>56.23</v>
+        <v>56.17</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>16</v>
@@ -5032,10 +5032,10 @@
         <v>2021</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>197</v>
@@ -5044,16 +5044,16 @@
         <v>198</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>56.17</v>
+        <v>56.08</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>16</v>
@@ -5064,10 +5064,10 @@
         <v>2021</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>199</v>
@@ -5076,16 +5076,16 @@
         <v>200</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>56.08</v>
+        <v>55.67</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>16</v>
@@ -5096,10 +5096,10 @@
         <v>2021</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>201</v>
@@ -5108,16 +5108,16 @@
         <v>202</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>55.67</v>
+        <v>55.63</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>16</v>
@@ -5128,10 +5128,10 @@
         <v>2021</v>
       </c>
       <c r="B92" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>203</v>
@@ -5140,16 +5140,16 @@
         <v>204</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>55.63</v>
+        <v>55.53</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>16</v>
@@ -5160,10 +5160,10 @@
         <v>2021</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>205</v>
@@ -5172,16 +5172,16 @@
         <v>206</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>55.53</v>
+        <v>55.15</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>16</v>
@@ -5192,10 +5192,10 @@
         <v>2021</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>178</v>
+        <v>39</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>207</v>
@@ -5204,16 +5204,16 @@
         <v>208</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>55.15</v>
+        <v>55.14</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>16</v>
@@ -5224,10 +5224,10 @@
         <v>2021</v>
       </c>
       <c r="B95" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>209</v>
@@ -5236,16 +5236,16 @@
         <v>210</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>55.14</v>
+        <v>55.13</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>16</v>
@@ -5256,10 +5256,10 @@
         <v>2021</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>211</v>
@@ -5268,16 +5268,16 @@
         <v>212</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>55.13</v>
+        <v>55.11</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>16</v>
@@ -5288,10 +5288,10 @@
         <v>2021</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>213</v>
@@ -5300,16 +5300,16 @@
         <v>214</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>55.11</v>
+        <v>54.99</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>16</v>
@@ -5320,10 +5320,10 @@
         <v>2021</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>215</v>
@@ -5332,16 +5332,16 @@
         <v>216</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>54.99</v>
+        <v>54.97</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>16</v>
@@ -5352,10 +5352,10 @@
         <v>2021</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>217</v>
@@ -5364,16 +5364,16 @@
         <v>218</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>54.97</v>
+        <v>54.95</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>16</v>
@@ -5384,10 +5384,10 @@
         <v>2021</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>219</v>
@@ -5396,16 +5396,16 @@
         <v>220</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>54.95</v>
+        <v>54.84</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>16</v>
@@ -5416,10 +5416,10 @@
         <v>2021</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>221</v>
@@ -5428,16 +5428,16 @@
         <v>222</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>54.84</v>
+        <v>54.83</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>16</v>
@@ -5451,7 +5451,7 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>223</v>
@@ -5460,16 +5460,16 @@
         <v>224</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>54.83</v>
+        <v>54.54</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>16</v>
@@ -5483,7 +5483,7 @@
         <v>13</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>225</v>
@@ -5492,16 +5492,16 @@
         <v>226</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>54.54</v>
+        <v>54.43</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>16</v>
@@ -5512,10 +5512,10 @@
         <v>2021</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>227</v>
@@ -5524,16 +5524,16 @@
         <v>228</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>54.43</v>
+        <v>54.4</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>16</v>
@@ -5544,10 +5544,10 @@
         <v>2021</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>229</v>
@@ -5556,16 +5556,16 @@
         <v>230</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>54.4</v>
+        <v>54.39</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>16</v>
@@ -5579,7 +5579,7 @@
         <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>231</v>
@@ -5588,16 +5588,16 @@
         <v>232</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>54.39</v>
+        <v>54.06</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>16</v>
@@ -5608,10 +5608,10 @@
         <v>2021</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>233</v>
@@ -5620,16 +5620,16 @@
         <v>234</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>54.06</v>
+        <v>53.87</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>16</v>
@@ -5640,10 +5640,10 @@
         <v>2021</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>235</v>
@@ -5652,16 +5652,16 @@
         <v>236</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>53.87</v>
+        <v>53.76</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>16</v>
@@ -5675,7 +5675,7 @@
         <v>6</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>237</v>
@@ -5684,10 +5684,10 @@
         <v>238</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -5704,10 +5704,10 @@
         <v>2021</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>239</v>
@@ -5716,16 +5716,16 @@
         <v>240</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>53.76</v>
+        <v>53.73</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>16</v>
@@ -5736,10 +5736,10 @@
         <v>2021</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>241</v>
@@ -5748,10 +5748,10 @@
         <v>242</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -5768,10 +5768,10 @@
         <v>2021</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>243</v>
@@ -5780,16 +5780,16 @@
         <v>244</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>53.73</v>
+        <v>53.56</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>16</v>
@@ -5800,10 +5800,10 @@
         <v>2021</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>245</v>
@@ -5812,16 +5812,16 @@
         <v>246</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>53.56</v>
+        <v>53.36</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>16</v>
@@ -5832,10 +5832,10 @@
         <v>2021</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>247</v>
@@ -5844,16 +5844,16 @@
         <v>248</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>53.36</v>
+        <v>53.31</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>16</v>
@@ -5864,10 +5864,10 @@
         <v>2021</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>249</v>
@@ -5876,16 +5876,16 @@
         <v>250</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>53.31</v>
+        <v>52.86</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>16</v>
@@ -5896,10 +5896,10 @@
         <v>2021</v>
       </c>
       <c r="B116" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>251</v>
@@ -5908,16 +5908,16 @@
         <v>252</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>52.86</v>
+        <v>52.59</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>16</v>
@@ -5928,10 +5928,10 @@
         <v>2021</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>253</v>
@@ -5940,16 +5940,16 @@
         <v>254</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>52.59</v>
+        <v>52.57</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>16</v>
@@ -5960,10 +5960,10 @@
         <v>2021</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>255</v>
@@ -5972,16 +5972,16 @@
         <v>256</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>52.57</v>
+        <v>52.46</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>16</v>
@@ -5995,7 +5995,7 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>257</v>
@@ -6004,16 +6004,16 @@
         <v>258</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>52.46</v>
+        <v>51.86</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>16</v>
@@ -6024,10 +6024,10 @@
         <v>2021</v>
       </c>
       <c r="B120" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>259</v>
@@ -6036,16 +6036,16 @@
         <v>260</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>51.86</v>
+        <v>51.84</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>16</v>
@@ -6056,10 +6056,10 @@
         <v>2021</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>261</v>
@@ -6068,16 +6068,16 @@
         <v>262</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>51.84</v>
+        <v>51.73</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>16</v>
@@ -6088,10 +6088,10 @@
         <v>2021</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>263</v>
@@ -6100,16 +6100,16 @@
         <v>264</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>51.73</v>
+        <v>51.72</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>16</v>
@@ -6120,10 +6120,10 @@
         <v>2021</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>265</v>
@@ -6132,16 +6132,16 @@
         <v>266</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>51.72</v>
+        <v>51.61</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>16</v>
@@ -6152,10 +6152,10 @@
         <v>2021</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>267</v>
@@ -6164,16 +6164,16 @@
         <v>268</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>51.61</v>
+        <v>51.56</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>16</v>
@@ -6184,10 +6184,10 @@
         <v>2021</v>
       </c>
       <c r="B125" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>269</v>
@@ -6196,16 +6196,16 @@
         <v>270</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>51.56</v>
+        <v>51.36</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>16</v>
@@ -6219,7 +6219,7 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>271</v>
@@ -6228,16 +6228,16 @@
         <v>272</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>51.36</v>
+        <v>51.31</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>16</v>
@@ -6248,10 +6248,10 @@
         <v>2021</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>273</v>
@@ -6260,16 +6260,16 @@
         <v>274</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>51.31</v>
+        <v>50.9</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>16</v>
@@ -6283,7 +6283,7 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>275</v>
@@ -6292,16 +6292,16 @@
         <v>276</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>50.9</v>
+        <v>50.57</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>16</v>
@@ -6312,10 +6312,10 @@
         <v>2021</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>277</v>
@@ -6324,16 +6324,16 @@
         <v>278</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>50.57</v>
+        <v>50.06</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>16</v>
@@ -6344,10 +6344,10 @@
         <v>2021</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>279</v>
@@ -6356,16 +6356,16 @@
         <v>280</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>50.06</v>
+        <v>49.87</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>16</v>
@@ -6379,7 +6379,7 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>281</v>
@@ -6388,16 +6388,16 @@
         <v>282</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>49.87</v>
+        <v>49.79</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>16</v>
@@ -6408,10 +6408,10 @@
         <v>2021</v>
       </c>
       <c r="B132" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>283</v>
@@ -6420,16 +6420,16 @@
         <v>284</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>49.79</v>
+        <v>49.29</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>16</v>
@@ -6440,10 +6440,10 @@
         <v>2021</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>285</v>
@@ -6452,16 +6452,16 @@
         <v>286</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>49.29</v>
+        <v>49.07</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>16</v>
@@ -6472,10 +6472,10 @@
         <v>2021</v>
       </c>
       <c r="B134" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>287</v>
@@ -6484,16 +6484,16 @@
         <v>288</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>49.07</v>
+        <v>48.77</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>16</v>
@@ -6507,7 +6507,7 @@
         <v>13</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>289</v>
@@ -6516,16 +6516,16 @@
         <v>290</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>48.77</v>
+        <v>48.72</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>16</v>
@@ -6536,10 +6536,10 @@
         <v>2021</v>
       </c>
       <c r="B136" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>291</v>
@@ -6548,16 +6548,16 @@
         <v>292</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>48.72</v>
+        <v>48.57</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>16</v>
@@ -6568,10 +6568,10 @@
         <v>2021</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>293</v>
@@ -6580,16 +6580,16 @@
         <v>294</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>48.57</v>
+        <v>48.03</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>16</v>
@@ -6600,10 +6600,10 @@
         <v>2021</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>295</v>
@@ -6612,16 +6612,16 @@
         <v>296</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>48.03</v>
+        <v>47.78</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>16</v>
@@ -6635,7 +6635,7 @@
         <v>5</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>297</v>
@@ -6644,16 +6644,16 @@
         <v>298</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>47.78</v>
+        <v>47.62</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>16</v>
@@ -6664,10 +6664,10 @@
         <v>2021</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>299</v>
@@ -6676,16 +6676,16 @@
         <v>300</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>47.62</v>
+        <v>47.58</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>16</v>
@@ -6696,10 +6696,10 @@
         <v>2021</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>178</v>
+        <v>50</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>301</v>
@@ -6708,16 +6708,16 @@
         <v>302</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>47.58</v>
+        <v>47.37</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>16</v>
@@ -6731,7 +6731,7 @@
         <v>6</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>303</v>
@@ -6740,16 +6740,16 @@
         <v>304</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>47.37</v>
+        <v>46.79</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>16</v>
@@ -6760,10 +6760,10 @@
         <v>2021</v>
       </c>
       <c r="B143" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>54</v>
+        <v>176</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>305</v>
@@ -6772,16 +6772,16 @@
         <v>306</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>46.79</v>
+        <v>45.86</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>16</v>
@@ -6795,7 +6795,7 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>307</v>
@@ -6804,16 +6804,16 @@
         <v>308</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>45.86</v>
+        <v>45.43</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>16</v>
@@ -6824,10 +6824,10 @@
         <v>2021</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>178</v>
+        <v>57</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>309</v>
@@ -6836,16 +6836,16 @@
         <v>310</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>45.43</v>
+        <v>43.56</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>16</v>
@@ -6856,10 +6856,10 @@
         <v>2021</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>61</v>
+        <v>176</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>311</v>
@@ -6868,16 +6868,16 @@
         <v>312</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>43.56</v>
+        <v>42.52</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>16</v>
@@ -6891,7 +6891,7 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>313</v>
@@ -6900,16 +6900,16 @@
         <v>314</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>42.52</v>
+        <v>41.39</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>16</v>
@@ -6923,7 +6923,7 @@
         <v>13</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>315</v>
@@ -6932,16 +6932,16 @@
         <v>316</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>41.39</v>
+        <v>38.41</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>16</v>
@@ -6955,7 +6955,7 @@
         <v>13</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>317</v>
@@ -6964,16 +6964,16 @@
         <v>318</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>38.41</v>
+        <v>38.29</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>16</v>
@@ -6984,28 +6984,28 @@
         <v>2021</v>
       </c>
       <c r="B150" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>41</v>
+        <v>322</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>42</v>
+        <v>323</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>38.29</v>
+        <v>76.34</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>16</v>
@@ -7016,28 +7016,28 @@
         <v>2021</v>
       </c>
       <c r="B151" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="D151" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F151" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="E151" s="2" t="s">
+      <c r="G151" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="F151" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>325</v>
-      </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>76.34</v>
+        <v>68.56</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>16</v>
@@ -7048,28 +7048,28 @@
         <v>2021</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>68.56</v>
+        <v>68.24</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>16</v>
@@ -7080,10 +7080,10 @@
         <v>2021</v>
       </c>
       <c r="B153" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>329</v>
+        <v>324</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>330</v>
@@ -7092,16 +7092,16 @@
         <v>331</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>68.24</v>
+        <v>66.99</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>16</v>
@@ -7115,7 +7115,7 @@
         <v>3</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>332</v>
@@ -7124,16 +7124,16 @@
         <v>333</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>66.99</v>
+        <v>66.62</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>16</v>
@@ -7144,28 +7144,28 @@
         <v>2021</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>66.62</v>
+        <v>65.1</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>16</v>
@@ -7176,10 +7176,10 @@
         <v>2021</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>336</v>
+        <v>324</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>337</v>
@@ -7188,16 +7188,16 @@
         <v>338</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>65.1</v>
+        <v>64.99</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>16</v>
@@ -7208,10 +7208,10 @@
         <v>2021</v>
       </c>
       <c r="B157" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>339</v>
@@ -7220,16 +7220,16 @@
         <v>340</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>64.99</v>
+        <v>63.67</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>16</v>
@@ -7243,7 +7243,7 @@
         <v>4</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>341</v>
@@ -7252,10 +7252,10 @@
         <v>342</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7275,7 +7275,7 @@
         <v>4</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>343</v>
@@ -7284,10 +7284,10 @@
         <v>344</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7307,7 +7307,7 @@
         <v>3</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>345</v>
@@ -7316,10 +7316,10 @@
         <v>346</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7339,7 +7339,7 @@
         <v>4</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>347</v>
@@ -7348,10 +7348,10 @@
         <v>348</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7371,7 +7371,7 @@
         <v>4</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>349</v>
@@ -7380,10 +7380,10 @@
         <v>350</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7412,10 +7412,10 @@
         <v>353</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7435,7 +7435,7 @@
         <v>15</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>354</v>
@@ -7444,10 +7444,10 @@
         <v>355</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7467,7 +7467,7 @@
         <v>4</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>356</v>
@@ -7476,10 +7476,10 @@
         <v>357</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7499,7 +7499,7 @@
         <v>15</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>358</v>
@@ -7508,10 +7508,10 @@
         <v>359</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7531,19 +7531,19 @@
         <v>4</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>360</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7563,7 +7563,7 @@
         <v>4</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>361</v>
@@ -7572,10 +7572,10 @@
         <v>362</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7595,7 +7595,7 @@
         <v>4</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>363</v>
@@ -7604,10 +7604,10 @@
         <v>364</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7627,7 +7627,7 @@
         <v>4</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>365</v>
@@ -7636,10 +7636,10 @@
         <v>366</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7659,7 +7659,7 @@
         <v>3</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>367</v>
@@ -7668,10 +7668,10 @@
         <v>368</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -7691,7 +7691,7 @@
         <v>4</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>369</v>
@@ -7700,10 +7700,10 @@
         <v>370</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -7723,7 +7723,7 @@
         <v>4</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>371</v>
@@ -7732,10 +7732,10 @@
         <v>372</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -7764,10 +7764,10 @@
         <v>374</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -7787,7 +7787,7 @@
         <v>4</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>375</v>
@@ -7796,10 +7796,10 @@
         <v>376</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -7819,7 +7819,7 @@
         <v>3</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>377</v>
@@ -7828,10 +7828,10 @@
         <v>378</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -7860,10 +7860,10 @@
         <v>380</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -7883,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>381</v>
@@ -7892,10 +7892,10 @@
         <v>382</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:11</t>
+    <t xml:space="preserve">2026-09-18 11:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_preneta_a_2021.xlsx
@@ -1789,7 +1789,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:31</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
